--- a/nmoreau/ig/CodeSystem-document-type-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-document-type-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-document-type-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-document-type-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-document-type-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-document-type-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>9</t>
+    <t>11</t>
   </si>
   <si>
     <t>Level</t>
@@ -193,6 +193,18 @@
   </si>
   <si>
     <t>Arrêt de travail</t>
+  </si>
+  <si>
+    <t>PERS_PREVENIR</t>
+  </si>
+  <si>
+    <t>Fiche de déclaration de la personne à prévenir</t>
+  </si>
+  <si>
+    <t>PERS_CONFIANCE</t>
+  </si>
+  <si>
+    <t>Fiche de déclaration de la personne de confiance</t>
   </si>
 </sst>
 </file>
@@ -510,7 +522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -635,6 +647,30 @@
       </c>
       <c r="D10" s="2"/>
     </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/nmoreau/ig/CodeSystem-document-type-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-document-type-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-document-type-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-document-type-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-document-type-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-document-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-document-type-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-document-type-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-document-type-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-document-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
